--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/85.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/85.xlsx
@@ -426,13 +426,13 @@
         <v>-7.344886050792672</v>
       </c>
       <c r="E2">
-        <v>-7.41604394994694</v>
+        <v>-5.781101808113664</v>
       </c>
       <c r="F2">
-        <v>-5.167430558977076</v>
+        <v>-4.505827596606959</v>
       </c>
       <c r="G2">
-        <v>-6.293652791012473</v>
+        <v>-5.696668735006779</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.394216999048105</v>
       </c>
       <c r="E3">
-        <v>-7.872831123100648</v>
+        <v>-6.756046034173031</v>
       </c>
       <c r="F3">
-        <v>-5.371238761292255</v>
+        <v>-4.78412590925148</v>
       </c>
       <c r="G3">
-        <v>-5.721514379279009</v>
+        <v>-5.510212189143947</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.619601373979489</v>
       </c>
       <c r="E4">
-        <v>-7.497683279357221</v>
+        <v>-7.465340917994439</v>
       </c>
       <c r="F4">
-        <v>-5.402202306441498</v>
+        <v>-4.977953941097731</v>
       </c>
       <c r="G4">
-        <v>-6.070750449307805</v>
+        <v>-5.797842317232446</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.004128969610331</v>
       </c>
       <c r="E5">
-        <v>-8.737914569733933</v>
+        <v>-7.747885996755016</v>
       </c>
       <c r="F5">
-        <v>-5.414704027284547</v>
+        <v>-4.991115042393409</v>
       </c>
       <c r="G5">
-        <v>-5.982729664509663</v>
+        <v>-6.105938237844718</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.511726226621091</v>
       </c>
       <c r="E6">
-        <v>-10.69054274862731</v>
+        <v>-8.821378874169305</v>
       </c>
       <c r="F6">
-        <v>-5.318152836283849</v>
+        <v>-4.683576188797468</v>
       </c>
       <c r="G6">
-        <v>-6.274696607254606</v>
+        <v>-5.784378328524229</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.089765654071675</v>
       </c>
       <c r="E7">
-        <v>-10.76467386813287</v>
+        <v>-10.59266431142552</v>
       </c>
       <c r="F7">
-        <v>-5.45915753558838</v>
+        <v>-4.826861383561907</v>
       </c>
       <c r="G7">
-        <v>-5.568610212456691</v>
+        <v>-6.032384537053192</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.689237928645468</v>
       </c>
       <c r="E8">
-        <v>-12.27130622743281</v>
+        <v>-11.80903054378181</v>
       </c>
       <c r="F8">
-        <v>-5.527891320835669</v>
+        <v>-4.597437576049958</v>
       </c>
       <c r="G8">
-        <v>-6.114704562432709</v>
+        <v>-5.680321261133858</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.25020891449402</v>
       </c>
       <c r="E9">
-        <v>-12.73625823922235</v>
+        <v>-11.25161162122965</v>
       </c>
       <c r="F9">
-        <v>-5.221151013416026</v>
+        <v>-4.444658462482034</v>
       </c>
       <c r="G9">
-        <v>-5.718114449010177</v>
+        <v>-5.657223584906363</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.72638255824439</v>
       </c>
       <c r="E10">
-        <v>-13.30957663401544</v>
+        <v>-12.53128139173916</v>
       </c>
       <c r="F10">
-        <v>-4.98310224450613</v>
+        <v>-4.690675297439459</v>
       </c>
       <c r="G10">
-        <v>-6.177753902228129</v>
+        <v>-4.99868324514346</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.07463310523879</v>
       </c>
       <c r="E11">
-        <v>-14.2470839654534</v>
+        <v>-13.97448341561367</v>
       </c>
       <c r="F11">
-        <v>-4.97109174553294</v>
+        <v>-4.224599348458734</v>
       </c>
       <c r="G11">
-        <v>-5.078430976638963</v>
+        <v>-5.088031558702849</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.27300147518736</v>
       </c>
       <c r="E12">
-        <v>-15.25028586932063</v>
+        <v>-14.81955100713305</v>
       </c>
       <c r="F12">
-        <v>-4.642854475643246</v>
+        <v>-4.423255933895904</v>
       </c>
       <c r="G12">
-        <v>-5.506799016692958</v>
+        <v>-5.192250842824646</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.31496816730862</v>
       </c>
       <c r="E13">
-        <v>-15.35344903568937</v>
+        <v>-16.14421116690876</v>
       </c>
       <c r="F13">
-        <v>-4.712892939549945</v>
+        <v>-4.021400824552016</v>
       </c>
       <c r="G13">
-        <v>-4.746462712143005</v>
+        <v>-4.024230786750064</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.2105941755108</v>
       </c>
       <c r="E14">
-        <v>-16.26819172829076</v>
+        <v>-16.30147601224714</v>
       </c>
       <c r="F14">
-        <v>-4.508247257790535</v>
+        <v>-3.850879737950932</v>
       </c>
       <c r="G14">
-        <v>-4.267029507145752</v>
+        <v>-3.453022638313135</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.98878661316398</v>
       </c>
       <c r="E15">
-        <v>-17.93020055926788</v>
+        <v>-17.91469053579161</v>
       </c>
       <c r="F15">
-        <v>-4.434105890137771</v>
+        <v>-3.920332546103851</v>
       </c>
       <c r="G15">
-        <v>-4.085906250146686</v>
+        <v>-3.650784697192578</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.68200157366662</v>
       </c>
       <c r="E16">
-        <v>-18.60744743253701</v>
+        <v>-19.10240511310137</v>
       </c>
       <c r="F16">
-        <v>-3.936278618607741</v>
+        <v>-3.4666174955077</v>
       </c>
       <c r="G16">
-        <v>-3.445683158852571</v>
+        <v>-2.531386623453272</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.33606886015842</v>
       </c>
       <c r="E17">
-        <v>-20.24749316457693</v>
+        <v>-19.30476450260813</v>
       </c>
       <c r="F17">
-        <v>-3.895324134213334</v>
+        <v>-3.242752861635939</v>
       </c>
       <c r="G17">
-        <v>-2.665185631968456</v>
+        <v>-2.408780569406364</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.990310349792516</v>
       </c>
       <c r="E18">
-        <v>-20.0111430491686</v>
+        <v>-20.61255156823127</v>
       </c>
       <c r="F18">
-        <v>-3.103761923487613</v>
+        <v>-3.091806096763008</v>
       </c>
       <c r="G18">
-        <v>-3.520597493860739</v>
+        <v>-1.796945406111499</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.684137769683785</v>
       </c>
       <c r="E19">
-        <v>-20.83716840748572</v>
+        <v>-21.95278515011936</v>
       </c>
       <c r="F19">
-        <v>-3.290342568926771</v>
+        <v>-2.813946818841969</v>
       </c>
       <c r="G19">
-        <v>-2.187848002297562</v>
+        <v>-1.139312155826356</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.443629171765419</v>
       </c>
       <c r="E20">
-        <v>-21.58852828636438</v>
+        <v>-22.66061733683629</v>
       </c>
       <c r="F20">
-        <v>-3.286981882373613</v>
+        <v>-2.621839306091333</v>
       </c>
       <c r="G20">
-        <v>-2.474657115092321</v>
+        <v>-1.398319307182316</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.284732657843977</v>
       </c>
       <c r="E21">
-        <v>-22.71072943020517</v>
+        <v>-24.12895691992738</v>
       </c>
       <c r="F21">
-        <v>-2.573546314875525</v>
+        <v>-2.241299746756282</v>
       </c>
       <c r="G21">
-        <v>-2.1555139040155</v>
+        <v>-1.041598093689228</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.214358649162067</v>
       </c>
       <c r="E22">
-        <v>-24.31546212193328</v>
+        <v>-23.93555032353378</v>
       </c>
       <c r="F22">
-        <v>-2.690127429675916</v>
+        <v>-2.100378712559433</v>
       </c>
       <c r="G22">
-        <v>-2.345671639791237</v>
+        <v>-0.4850093143537199</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.220863704593329</v>
       </c>
       <c r="E23">
-        <v>-24.4252866735673</v>
+        <v>-24.81349916482286</v>
       </c>
       <c r="F23">
-        <v>-2.768633465174031</v>
+        <v>-2.039258452111275</v>
       </c>
       <c r="G23">
-        <v>-1.851834251152615</v>
+        <v>-1.201156457045481</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.290211400824738</v>
       </c>
       <c r="E24">
-        <v>-25.15622766314537</v>
+        <v>-26.16760346259645</v>
       </c>
       <c r="F24">
-        <v>-2.333093623762704</v>
+        <v>-1.77920741661562</v>
       </c>
       <c r="G24">
-        <v>-2.148522031836559</v>
+        <v>-0.8298456693608246</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.392149102255805</v>
       </c>
       <c r="E25">
-        <v>-24.2528921965693</v>
+        <v>-26.18930843851521</v>
       </c>
       <c r="F25">
-        <v>-2.458328692820142</v>
+        <v>-1.781338805943024</v>
       </c>
       <c r="G25">
-        <v>-2.6259225618727</v>
+        <v>-1.475296112061449</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.500385342617772</v>
       </c>
       <c r="E26">
-        <v>-26.15630491994731</v>
+        <v>-26.37741672031983</v>
       </c>
       <c r="F26">
-        <v>-1.841723476137496</v>
+        <v>-1.364378417009087</v>
       </c>
       <c r="G26">
-        <v>-2.552799232001278</v>
+        <v>-1.423313926003813</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.584475283035674</v>
       </c>
       <c r="E27">
-        <v>-26.459581352715</v>
+        <v>-26.03753210367413</v>
       </c>
       <c r="F27">
-        <v>-2.258751791198462</v>
+        <v>-1.524299714323948</v>
       </c>
       <c r="G27">
-        <v>-3.665102806649926</v>
+        <v>-1.498605663203458</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.620677228884944</v>
       </c>
       <c r="E28">
-        <v>-25.20840474066175</v>
+        <v>-26.12032166548236</v>
       </c>
       <c r="F28">
-        <v>-2.124724430527711</v>
+        <v>-1.607091722764147</v>
       </c>
       <c r="G28">
-        <v>-3.018914112294043</v>
+        <v>-1.468436661704079</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.59353855088804</v>
       </c>
       <c r="E29">
-        <v>-25.40318799315368</v>
+        <v>-26.49799639772207</v>
       </c>
       <c r="F29">
-        <v>-2.158329639324481</v>
+        <v>-1.706469303343199</v>
       </c>
       <c r="G29">
-        <v>-3.27752730873083</v>
+        <v>-2.296576249443846</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.49174826713025</v>
       </c>
       <c r="E30">
-        <v>-24.73674153039284</v>
+        <v>-26.26746084293959</v>
       </c>
       <c r="F30">
-        <v>-2.223582624745207</v>
+        <v>-1.594588345186292</v>
       </c>
       <c r="G30">
-        <v>-2.28978963108834</v>
+        <v>-2.155341755647458</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.318857682974087</v>
       </c>
       <c r="E31">
-        <v>-25.13884737990394</v>
+        <v>-25.73961738413152</v>
       </c>
       <c r="F31">
-        <v>-2.376556404652789</v>
+        <v>-1.842840943763873</v>
       </c>
       <c r="G31">
-        <v>-4.137881815113244</v>
+        <v>-2.082622312331827</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.077419757485348</v>
       </c>
       <c r="E32">
-        <v>-24.86935789170747</v>
+        <v>-26.23011451779833</v>
       </c>
       <c r="F32">
-        <v>-2.383463332057331</v>
+        <v>-1.796103626530522</v>
       </c>
       <c r="G32">
-        <v>-3.234311447261184</v>
+        <v>-1.898327552706139</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.78109213588416</v>
       </c>
       <c r="E33">
-        <v>-23.86846098111015</v>
+        <v>-26.02527805300938</v>
       </c>
       <c r="F33">
-        <v>-2.024693268067851</v>
+        <v>-1.712535437833899</v>
       </c>
       <c r="G33">
-        <v>-3.745231250882445</v>
+        <v>-2.337501213400316</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.442784866136771</v>
       </c>
       <c r="E34">
-        <v>-23.68245391124509</v>
+        <v>-25.05966701187982</v>
       </c>
       <c r="F34">
-        <v>-2.000167794373166</v>
+        <v>-2.005035281232016</v>
       </c>
       <c r="G34">
-        <v>-3.349607816757382</v>
+        <v>-1.583954837751408</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.078064754873278</v>
       </c>
       <c r="E35">
-        <v>-24.33535117977497</v>
+        <v>-24.72564224060005</v>
       </c>
       <c r="F35">
-        <v>-2.50960132158382</v>
+        <v>-2.043271892177838</v>
       </c>
       <c r="G35">
-        <v>-3.239081943383274</v>
+        <v>-2.079447499159666</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.705907857222042</v>
       </c>
       <c r="E36">
-        <v>-22.50120146634427</v>
+        <v>-24.01194115156918</v>
       </c>
       <c r="F36">
-        <v>-2.421786921580447</v>
+        <v>-1.953201847736642</v>
       </c>
       <c r="G36">
-        <v>-3.739212679092051</v>
+        <v>-0.984729542415627</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.341082648784158</v>
       </c>
       <c r="E37">
-        <v>-22.48619863195686</v>
+        <v>-23.55408978702366</v>
       </c>
       <c r="F37">
-        <v>-2.289944794118281</v>
+        <v>-1.823394190615752</v>
       </c>
       <c r="G37">
-        <v>-3.459604002845206</v>
+        <v>-2.050510020600897</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.004509861814591</v>
       </c>
       <c r="E38">
-        <v>-22.56814136912566</v>
+        <v>-23.25966199246696</v>
       </c>
       <c r="F38">
-        <v>-2.354195454981619</v>
+        <v>-2.160074181074777</v>
       </c>
       <c r="G38">
-        <v>-2.922309082912571</v>
+        <v>-1.401424598898152</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.707774486391553</v>
       </c>
       <c r="E39">
-        <v>-22.43476875265175</v>
+        <v>-23.01769204081511</v>
       </c>
       <c r="F39">
-        <v>-2.26985025766117</v>
+        <v>-2.14307856707154</v>
       </c>
       <c r="G39">
-        <v>-2.488660722723438</v>
+        <v>-0.8900777349023246</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.464905150776358</v>
       </c>
       <c r="E40">
-        <v>-22.30470645067745</v>
+        <v>-22.59096034965031</v>
       </c>
       <c r="F40">
-        <v>-2.582414816289897</v>
+        <v>-2.263879385421792</v>
       </c>
       <c r="G40">
-        <v>-1.732356662640318</v>
+        <v>-1.090435261484556</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.283847441264185</v>
       </c>
       <c r="E41">
-        <v>-21.17602053205767</v>
+        <v>-21.28147510627429</v>
       </c>
       <c r="F41">
-        <v>-2.437790979802533</v>
+        <v>-2.171357373468309</v>
       </c>
       <c r="G41">
-        <v>-1.649798277981973</v>
+        <v>-0.2048841930027491</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.166809243453804</v>
       </c>
       <c r="E42">
-        <v>-20.39613126693069</v>
+        <v>-20.66607360252792</v>
       </c>
       <c r="F42">
-        <v>-2.176713597094811</v>
+        <v>-2.318760382592064</v>
       </c>
       <c r="G42">
-        <v>-1.822138657665352</v>
+        <v>-0.3928536581770279</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.11263481435722</v>
       </c>
       <c r="E43">
-        <v>-19.78174866983605</v>
+        <v>-20.99286640081745</v>
       </c>
       <c r="F43">
-        <v>-2.474046964288263</v>
+        <v>-2.121091211099032</v>
       </c>
       <c r="G43">
-        <v>-1.891385338710288</v>
+        <v>-0.4683009910170182</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.109035799588657</v>
       </c>
       <c r="E44">
-        <v>-18.97078501606843</v>
+        <v>-19.16339007256267</v>
       </c>
       <c r="F44">
-        <v>-2.790590171552635</v>
+        <v>-2.229682722299422</v>
       </c>
       <c r="G44">
-        <v>-1.059908721066936</v>
+        <v>0.1436632835538785</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.146017048100211</v>
       </c>
       <c r="E45">
-        <v>-18.5459235846688</v>
+        <v>-19.34917977567536</v>
       </c>
       <c r="F45">
-        <v>-2.829544148669282</v>
+        <v>-2.390334639663553</v>
       </c>
       <c r="G45">
-        <v>-0.6267337688899194</v>
+        <v>0.1378930026789288</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.206874205857766</v>
       </c>
       <c r="E46">
-        <v>-19.1057878831851</v>
+        <v>-18.3957910858925</v>
       </c>
       <c r="F46">
-        <v>-2.667371348753611</v>
+        <v>-2.147157448162924</v>
       </c>
       <c r="G46">
-        <v>-1.096543218004511</v>
+        <v>0.6691527980934726</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.279124140469477</v>
       </c>
       <c r="E47">
-        <v>-17.52698070515091</v>
+        <v>-18.05866883839148</v>
       </c>
       <c r="F47">
-        <v>-3.009808492662093</v>
+        <v>-2.341323453909517</v>
       </c>
       <c r="G47">
-        <v>-1.144410395956833</v>
+        <v>0.6293765934391292</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.353028849026497</v>
       </c>
       <c r="E48">
-        <v>-17.7179102262623</v>
+        <v>-17.29342465820531</v>
       </c>
       <c r="F48">
-        <v>-2.935451749484601</v>
+        <v>-2.428227478137214</v>
       </c>
       <c r="G48">
-        <v>-1.044236598484027</v>
+        <v>0.6968090955285441</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.418768476299137</v>
       </c>
       <c r="E49">
-        <v>-16.2337345695664</v>
+        <v>-16.59575436716159</v>
       </c>
       <c r="F49">
-        <v>-3.074626585196349</v>
+        <v>-2.356111468784294</v>
       </c>
       <c r="G49">
-        <v>-1.617103330236131</v>
+        <v>0.104251238908855</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.476377992169794</v>
       </c>
       <c r="E50">
-        <v>-15.55807266219996</v>
+        <v>-16.22134919315542</v>
       </c>
       <c r="F50">
-        <v>-2.874329003934234</v>
+        <v>-2.704561731669698</v>
       </c>
       <c r="G50">
-        <v>-0.8661789066543258</v>
+        <v>0.4902277433324828</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.525592993825025</v>
       </c>
       <c r="E51">
-        <v>-15.75909162340045</v>
+        <v>-15.5282843601775</v>
       </c>
       <c r="F51">
-        <v>-2.914488255621954</v>
+        <v>-2.461018401777032</v>
       </c>
       <c r="G51">
-        <v>-1.624863248980182</v>
+        <v>0.7903717335594264</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.576001031071876</v>
       </c>
       <c r="E52">
-        <v>-15.15294632052575</v>
+        <v>-15.28156403929161</v>
       </c>
       <c r="F52">
-        <v>-3.033515539362812</v>
+        <v>-2.644843897234479</v>
       </c>
       <c r="G52">
-        <v>-2.407092191181336</v>
+        <v>0.6626707499275796</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.639457128762964</v>
       </c>
       <c r="E53">
-        <v>-15.15058698556776</v>
+        <v>-14.79900532056025</v>
       </c>
       <c r="F53">
-        <v>-3.29109969673293</v>
+        <v>-2.701232523077846</v>
       </c>
       <c r="G53">
-        <v>-0.7049056807087299</v>
+        <v>0.8340245870402563</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.728410942037949</v>
       </c>
       <c r="E54">
-        <v>-14.47220346532271</v>
+        <v>-13.56024125576202</v>
       </c>
       <c r="F54">
-        <v>-3.04933652838888</v>
+        <v>-2.671438632701356</v>
       </c>
       <c r="G54">
-        <v>-0.9212862477010341</v>
+        <v>0.3909544142463576</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.859972064683055</v>
       </c>
       <c r="E55">
-        <v>-13.73138587393391</v>
+        <v>-13.13416166485432</v>
       </c>
       <c r="F55">
-        <v>-2.98817153610097</v>
+        <v>-2.915765598157071</v>
       </c>
       <c r="G55">
-        <v>-1.423664843830976</v>
+        <v>0.5475432182538847</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.039539353424277</v>
       </c>
       <c r="E56">
-        <v>-13.24220652620333</v>
+        <v>-12.28809328057925</v>
       </c>
       <c r="F56">
-        <v>-2.8945287430515</v>
+        <v>-2.805978752794441</v>
       </c>
       <c r="G56">
-        <v>-1.284218044625795</v>
+        <v>0.1336488832975832</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.274729384040884</v>
       </c>
       <c r="E57">
-        <v>-12.2685846145542</v>
+        <v>-12.80124636970643</v>
       </c>
       <c r="F57">
-        <v>-3.184843353241031</v>
+        <v>-3.04038850370384</v>
       </c>
       <c r="G57">
-        <v>-1.459498188748047</v>
+        <v>0.4791639001402384</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.561320547686509</v>
       </c>
       <c r="E58">
-        <v>-12.75397815801437</v>
+        <v>-11.18151537206492</v>
       </c>
       <c r="F58">
-        <v>-3.181422195867469</v>
+        <v>-2.853160074955693</v>
       </c>
       <c r="G58">
-        <v>-1.863613172181342</v>
+        <v>0.4848315541034707</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.893668209319005</v>
       </c>
       <c r="E59">
-        <v>-11.6101263799429</v>
+        <v>-11.24683408115156</v>
       </c>
       <c r="F59">
-        <v>-3.5960134540294</v>
+        <v>-3.043088153069563</v>
       </c>
       <c r="G59">
-        <v>-1.689905537190243</v>
+        <v>0.5178641774943186</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.263828872360444</v>
       </c>
       <c r="E60">
-        <v>-11.13287956122254</v>
+        <v>-10.78785965505214</v>
       </c>
       <c r="F60">
-        <v>-3.518976113936448</v>
+        <v>-2.813386842477677</v>
       </c>
       <c r="G60">
-        <v>-1.885270761099254</v>
+        <v>0.2953425485266665</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.659163658538322</v>
       </c>
       <c r="E61">
-        <v>-10.43626440462261</v>
+        <v>-10.29224987423068</v>
       </c>
       <c r="F61">
-        <v>-3.490385013028823</v>
+        <v>-2.933652535485721</v>
       </c>
       <c r="G61">
-        <v>-2.229322516813551</v>
+        <v>-0.171457614692728</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.076892632437938</v>
       </c>
       <c r="E62">
-        <v>-10.51919887759908</v>
+        <v>-9.836902755811405</v>
       </c>
       <c r="F62">
-        <v>-3.320070189911037</v>
+        <v>-2.782467200800783</v>
       </c>
       <c r="G62">
-        <v>-2.022214787876746</v>
+        <v>0.05764537880699527</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.505321725480622</v>
       </c>
       <c r="E63">
-        <v>-10.52300279576553</v>
+        <v>-8.902189492836182</v>
       </c>
       <c r="F63">
-        <v>-3.301044247403538</v>
+        <v>-2.852280348773919</v>
       </c>
       <c r="G63">
-        <v>-2.151216815905526</v>
+        <v>-1.042657468261794</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.943109749779856</v>
       </c>
       <c r="E64">
-        <v>-10.43228840444387</v>
+        <v>-9.935682359340719</v>
       </c>
       <c r="F64">
-        <v>-3.325669125186558</v>
+        <v>-3.073953122497873</v>
       </c>
       <c r="G64">
-        <v>-1.509381488933786</v>
+        <v>-0.4885681508084364</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.38218373855362</v>
       </c>
       <c r="E65">
-        <v>-10.38549115404861</v>
+        <v>-9.635951721721034</v>
       </c>
       <c r="F65">
-        <v>-3.286671244597563</v>
+        <v>-3.094070024874859</v>
       </c>
       <c r="G65">
-        <v>-2.616696071454752</v>
+        <v>-0.8155110071757803</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.81589492918373</v>
       </c>
       <c r="E66">
-        <v>-9.936130678267478</v>
+        <v>-8.943244638189721</v>
       </c>
       <c r="F66">
-        <v>-3.365747196868804</v>
+        <v>-2.630186764409344</v>
       </c>
       <c r="G66">
-        <v>-2.830279227466372</v>
+        <v>-0.9250801328890388</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.23684996684895</v>
       </c>
       <c r="E67">
-        <v>-9.082694466781923</v>
+        <v>-8.086869447073187</v>
       </c>
       <c r="F67">
-        <v>-3.522986240533401</v>
+        <v>-3.110233958005685</v>
       </c>
       <c r="G67">
-        <v>-2.586781981961897</v>
+        <v>-0.8580151013544831</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.63160569064466</v>
       </c>
       <c r="E68">
-        <v>-10.23439409030868</v>
+        <v>-8.486303496919753</v>
       </c>
       <c r="F68">
-        <v>-3.374930477896239</v>
+        <v>-2.861216776315321</v>
       </c>
       <c r="G68">
-        <v>-3.142139238356796</v>
+        <v>-0.9896920501789945</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.99421521871779</v>
       </c>
       <c r="E69">
-        <v>-9.281254466596245</v>
+        <v>-8.010637115628066</v>
       </c>
       <c r="F69">
-        <v>-3.694025056761234</v>
+        <v>-2.832223917217338</v>
       </c>
       <c r="G69">
-        <v>-2.694225737438944</v>
+        <v>-1.167140601629469</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.3077165711214</v>
       </c>
       <c r="E70">
-        <v>-9.419463493310344</v>
+        <v>-8.391314226134858</v>
       </c>
       <c r="F70">
-        <v>-3.965069356059441</v>
+        <v>-2.926348820095237</v>
       </c>
       <c r="G70">
-        <v>-2.941245403397202</v>
+        <v>-1.243385775944424</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.56369854894377</v>
       </c>
       <c r="E71">
-        <v>-8.616479010744245</v>
+        <v>-7.753777541438995</v>
       </c>
       <c r="F71">
-        <v>-3.486937347898372</v>
+        <v>-3.313353787009138</v>
       </c>
       <c r="G71">
-        <v>-3.010081576795268</v>
+        <v>-1.626756881028645</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.74701184597037</v>
       </c>
       <c r="E72">
-        <v>-8.783289879290789</v>
+        <v>-7.496102841928544</v>
       </c>
       <c r="F72">
-        <v>-3.743753608686094</v>
+        <v>-3.075334010958339</v>
       </c>
       <c r="G72">
-        <v>-2.972407568558362</v>
+        <v>-1.387742114184344</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.8491900046576</v>
       </c>
       <c r="E73">
-        <v>-9.817158609137962</v>
+        <v>-8.554470616157214</v>
       </c>
       <c r="F73">
-        <v>-3.8728554967798</v>
+        <v>-3.295495014172184</v>
       </c>
       <c r="G73">
-        <v>-2.912682016484371</v>
+        <v>-1.228230098465641</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.86351466032476</v>
       </c>
       <c r="E74">
-        <v>-10.29205062137434</v>
+        <v>-8.102465511555605</v>
       </c>
       <c r="F74">
-        <v>-3.730057382048207</v>
+        <v>-3.282758865354142</v>
       </c>
       <c r="G74">
-        <v>-2.887329858744632</v>
+        <v>-1.13252553747085</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.78649766599569</v>
       </c>
       <c r="E75">
-        <v>-9.541415298336908</v>
+        <v>-8.247806884831785</v>
       </c>
       <c r="F75">
-        <v>-3.652482431510839</v>
+        <v>-3.403254844500163</v>
       </c>
       <c r="G75">
-        <v>-2.613061092452632</v>
+        <v>-0.5760724905024525</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.62353339993822</v>
       </c>
       <c r="E76">
-        <v>-10.78817211975867</v>
+        <v>-8.384050553826555</v>
       </c>
       <c r="F76">
-        <v>-3.879477465797779</v>
+        <v>-3.733331918391474</v>
       </c>
       <c r="G76">
-        <v>-1.826200697042038</v>
+        <v>-0.09043532316460492</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.37721028468779</v>
       </c>
       <c r="E77">
-        <v>-9.572086652790858</v>
+        <v>-9.305033483610522</v>
       </c>
       <c r="F77">
-        <v>-3.616903223193197</v>
+        <v>-3.747346238112036</v>
       </c>
       <c r="G77">
-        <v>-1.212365964241453</v>
+        <v>-0.3896225657306992</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.06227514272832</v>
       </c>
       <c r="E78">
-        <v>-10.09345439376795</v>
+        <v>-9.714226394943616</v>
       </c>
       <c r="F78">
-        <v>-4.031225261949218</v>
+        <v>-3.800577127415932</v>
       </c>
       <c r="G78">
-        <v>-1.656369710877426</v>
+        <v>-0.6974867481552233</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.68807446371988</v>
       </c>
       <c r="E79">
-        <v>-12.2278464623812</v>
+        <v>-9.816578964464981</v>
       </c>
       <c r="F79">
-        <v>-4.084110722046146</v>
+        <v>-3.532187745643698</v>
       </c>
       <c r="G79">
-        <v>-1.529738033454764</v>
+        <v>0.6764691037352619</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.27487342510365</v>
       </c>
       <c r="E80">
-        <v>-12.03798113266161</v>
+        <v>-9.908900964059356</v>
       </c>
       <c r="F80">
-        <v>-4.348738487442269</v>
+        <v>-4.164628033598259</v>
       </c>
       <c r="G80">
-        <v>-1.713781191619467</v>
+        <v>-0.2071320534239143</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.84005324623628</v>
       </c>
       <c r="E81">
-        <v>-11.634978645297</v>
+        <v>-11.17320109378684</v>
       </c>
       <c r="F81">
-        <v>-4.425074200345049</v>
+        <v>-4.069236556961479</v>
       </c>
       <c r="G81">
-        <v>-1.256101581360765</v>
+        <v>0.9042545001103552</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.40346937931093</v>
       </c>
       <c r="E82">
-        <v>-13.27488399464268</v>
+        <v>-11.54163321057689</v>
       </c>
       <c r="F82">
-        <v>-4.64966696916387</v>
+        <v>-3.981155422654405</v>
       </c>
       <c r="G82">
-        <v>-1.999173390923418</v>
+        <v>1.050981188956394</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.985972673113846</v>
       </c>
       <c r="E83">
-        <v>-13.53902535503608</v>
+        <v>-12.94154755141207</v>
       </c>
       <c r="F83">
-        <v>-4.671507704106082</v>
+        <v>-4.272167518197093</v>
       </c>
       <c r="G83">
-        <v>-1.337534380535757</v>
+        <v>1.239328056322149</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.59917331099016</v>
       </c>
       <c r="E84">
-        <v>-14.47374767495932</v>
+        <v>-14.07892814012657</v>
       </c>
       <c r="F84">
-        <v>-4.503720229934236</v>
+        <v>-4.407970898579447</v>
       </c>
       <c r="G84">
-        <v>-0.6570252605742508</v>
+        <v>1.275906273985556</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.259706721220828</v>
       </c>
       <c r="E85">
-        <v>-15.55493442971264</v>
+        <v>-14.60561230958868</v>
       </c>
       <c r="F85">
-        <v>-4.892029047140143</v>
+        <v>-4.508256369831966</v>
       </c>
       <c r="G85">
-        <v>-0.09528858292517649</v>
+        <v>1.001750066241892</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.970674723119815</v>
       </c>
       <c r="E86">
-        <v>-16.52152362122786</v>
+        <v>-16.2332047381075</v>
       </c>
       <c r="F86">
-        <v>-4.774780268213096</v>
+        <v>-4.654166660895877</v>
       </c>
       <c r="G86">
-        <v>-0.5632805425387086</v>
+        <v>1.605325418416275</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.739684078152052</v>
       </c>
       <c r="E87">
-        <v>-17.90303877216988</v>
+        <v>-16.85436193231762</v>
       </c>
       <c r="F87">
-        <v>-4.760509982965069</v>
+        <v>-4.75827918954933</v>
       </c>
       <c r="G87">
-        <v>0.007381365884240833</v>
+        <v>1.405434678755081</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.567660792352276</v>
       </c>
       <c r="E88">
-        <v>-19.00501575109241</v>
+        <v>-18.6285818207308</v>
       </c>
       <c r="F88">
-        <v>-5.130266683817879</v>
+        <v>-4.791550566282772</v>
       </c>
       <c r="G88">
-        <v>-0.4472856479337247</v>
+        <v>2.072039507451648</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.452786795119993</v>
       </c>
       <c r="E89">
-        <v>-21.55049816164797</v>
+        <v>-19.8814384966409</v>
       </c>
       <c r="F89">
-        <v>-5.211132738046569</v>
+        <v>-5.14264746302012</v>
       </c>
       <c r="G89">
-        <v>-0.514406958742448</v>
+        <v>1.649709902461284</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.39406061413788</v>
       </c>
       <c r="E90">
-        <v>-22.10899938948796</v>
+        <v>-21.41470734005396</v>
       </c>
       <c r="F90">
-        <v>-5.330632191207023</v>
+        <v>-5.1316044971734</v>
       </c>
       <c r="G90">
-        <v>-0.6903260381537797</v>
+        <v>2.158037548925296</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.380921999285738</v>
       </c>
       <c r="E91">
-        <v>-25.0108319481811</v>
+        <v>-23.26926688583723</v>
       </c>
       <c r="F91">
-        <v>-4.964646218771756</v>
+        <v>-4.967591064888709</v>
       </c>
       <c r="G91">
-        <v>-0.3548552164772732</v>
+        <v>1.595516271983415</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.409766071936742</v>
       </c>
       <c r="E92">
-        <v>-26.6898904837971</v>
+        <v>-25.35362384513973</v>
       </c>
       <c r="F92">
-        <v>-5.088536847534451</v>
+        <v>-5.108419321936444</v>
       </c>
       <c r="G92">
-        <v>-0.4955070542587489</v>
+        <v>1.711117211669225</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.468831354513284</v>
       </c>
       <c r="E93">
-        <v>-28.6721711104927</v>
+        <v>-27.63619664023196</v>
       </c>
       <c r="F93">
-        <v>-5.020471554781221</v>
+        <v>-5.054939094044306</v>
       </c>
       <c r="G93">
-        <v>-1.087925867965788</v>
+        <v>0.9730377047797927</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.5495368450272</v>
       </c>
       <c r="E94">
-        <v>-30.72721525754355</v>
+        <v>-29.76676441254573</v>
       </c>
       <c r="F94">
-        <v>-5.310045604512649</v>
+        <v>-5.288659643274575</v>
       </c>
       <c r="G94">
-        <v>-1.275653663315701</v>
+        <v>1.182303909408203</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.644633973175811</v>
       </c>
       <c r="E95">
-        <v>-32.98348667559923</v>
+        <v>-31.41730035462442</v>
       </c>
       <c r="F95">
-        <v>-5.183980511317607</v>
+        <v>-5.419363593925295</v>
       </c>
       <c r="G95">
-        <v>-1.460521147319682</v>
+        <v>0.8937335863865513</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.74272898714586</v>
       </c>
       <c r="E96">
-        <v>-35.33135327317106</v>
+        <v>-34.03335903258952</v>
       </c>
       <c r="F96">
-        <v>-5.392055634124606</v>
+        <v>-5.416963813559385</v>
       </c>
       <c r="G96">
-        <v>-2.312463557486808</v>
+        <v>0.4804417707183971</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.839830587789677</v>
       </c>
       <c r="E97">
-        <v>-37.10659886094699</v>
+        <v>-36.64535114089572</v>
       </c>
       <c r="F97">
-        <v>-5.616441311092728</v>
+        <v>-5.535411240118283</v>
       </c>
       <c r="G97">
-        <v>-2.408916301773474</v>
+        <v>0.3491190502665877</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.923977461034186</v>
       </c>
       <c r="E98">
-        <v>-39.53602553963396</v>
+        <v>-39.07193620214289</v>
       </c>
       <c r="F98">
-        <v>-5.419401698825824</v>
+        <v>-5.467595285953296</v>
       </c>
       <c r="G98">
-        <v>-2.409081829050438</v>
+        <v>-0.9619662312875984</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.993840259196233</v>
       </c>
       <c r="E99">
-        <v>-42.70914991917862</v>
+        <v>-41.97159735754935</v>
       </c>
       <c r="F99">
-        <v>-5.958370665783294</v>
+        <v>-5.939892274129045</v>
       </c>
       <c r="G99">
-        <v>-2.91077845279929</v>
+        <v>-0.9254740878082121</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.040840627856522</v>
       </c>
       <c r="E100">
-        <v>-44.76168302739222</v>
+        <v>-44.19709553048591</v>
       </c>
       <c r="F100">
-        <v>-5.606704680640223</v>
+        <v>-5.668163743356127</v>
       </c>
       <c r="G100">
-        <v>-3.357069786402899</v>
+        <v>-1.727764935977349</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.06596043685742</v>
       </c>
       <c r="E101">
-        <v>-47.22487853675439</v>
+        <v>-46.79696264963658</v>
       </c>
       <c r="F101">
-        <v>-5.899999756745027</v>
+        <v>-5.990117018128182</v>
       </c>
       <c r="G101">
-        <v>-4.455349890147194</v>
+        <v>-2.364687413368811</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.063422809780366</v>
       </c>
       <c r="E102">
-        <v>-49.9961563219249</v>
+        <v>-49.03745460001254</v>
       </c>
       <c r="F102">
-        <v>-5.346566666567274</v>
+        <v>-5.795265124172071</v>
       </c>
       <c r="G102">
-        <v>-5.07621953221873</v>
+        <v>-2.420046355876504</v>
       </c>
     </row>
   </sheetData>
